--- a/files/港岛-半山区西部-帝汇豪庭.xlsx
+++ b/files/港岛-半山区西部-帝汇豪庭.xlsx
@@ -1052,7 +1052,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2022-10-26</t>
+          <t>2022-10-27</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2016-06-14</t>
+          <t>2016-06-15</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2016-04-10</t>
+          <t>2016-04-11</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2016-07-12</t>
+          <t>2016-07-13</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2016-06-05</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2023-05-22</t>
+          <t>2023-05-23</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2016-02-21</t>
+          <t>2016-02-22</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2016-02-21</t>
+          <t>2016-02-22</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2024-07-08</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4470,7 +4470,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2016-03-01</t>
+          <t>2016-03-02</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2024-05-28</t>
+          <t>2024-05-29</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2016-02-21</t>
+          <t>2016-02-22</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4726,7 +4726,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2016-02-21</t>
+          <t>2016-02-22</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-02</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4850,7 +4850,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2016-02-21</t>
+          <t>2016-02-22</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5394,7 +5394,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2024-10-31</t>
+          <t>2024-11-01</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2016-02-21</t>
+          <t>2016-02-22</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2016-02-21</t>
+          <t>2016-02-22</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2024-11-03</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2016-01-23</t>
+          <t>2016-01-24</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2016-02-24</t>
+          <t>2016-02-25</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2016-04-27</t>
+          <t>2016-04-28</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2024-04-23</t>
+          <t>2024-04-24</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2016-06-19</t>
+          <t>2016-06-20</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2016-03-17</t>
+          <t>2016-03-18</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6434,7 +6434,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2016-02-21</t>
+          <t>2016-02-22</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6558,7 +6558,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2016-02-21</t>
+          <t>2016-02-22</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6921,7 +6921,7 @@
           <t>B | 2674呎 (3房)
 $15700万
 $58,714/呎
-(25年-07月-03日)</t>
+(25年-07月-04日)</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr"/>
@@ -7016,7 +7016,7 @@
           <t>A | 1735呎 (4+房)
 $6950万
 $40,058/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -7024,7 +7024,7 @@
           <t>B | 1024呎 (2房)
 $4180万
 $40,820/呎
-(24年-11月-06日)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">
@@ -7055,7 +7055,7 @@
           <t>A | 1735呎 (4+房)
 $6680万
 $38,500/呎
-(22年-10月-26日)</t>
+(22年-10月-27日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -7063,7 +7063,7 @@
           <t>B | 1024呎 (2房)
 $3990万
 $38,962/呎
-(25年-10月-20日)</t>
+(25年-10月-21日)</t>
         </is>
       </c>
       <c r="D11" s="20" t="inlineStr">
@@ -7094,7 +7094,7 @@
           <t>A | 1735呎 (4+房)
 $6520万
 $37,579/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -7110,7 +7110,7 @@
           <t>C | 1179呎 (3房)
 $3042万
 $25,800/呎
-(16年-06月-14日)</t>
+(16年-06月-15日)</t>
         </is>
       </c>
       <c r="E12" s="20" t="inlineStr">
@@ -7133,7 +7133,7 @@
           <t>A | 1735呎 (4+房)
 $6519万
 $37,572/呎
-(25年-03月-05日)</t>
+(25年-03月-06日)</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -7149,7 +7149,7 @@
           <t>C | 1179呎 (3房)
 $2988万
 $25,344/呎
-(16年-04月-10日)</t>
+(16年-04月-11日)</t>
         </is>
       </c>
       <c r="E13" s="20" t="inlineStr">
@@ -7172,7 +7172,7 @@
           <t>A | 1735呎 (4+房)
 $6350万
 $36,600/呎
-(25年-10月-01日)</t>
+(25年-10月-02日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -7180,7 +7180,7 @@
           <t>B | 1023呎 (2房)
 $2660万
 $26,000/呎
-(16年-06月-05日)</t>
+(16年-06月-06日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -7188,7 +7188,7 @@
           <t>C | 1179呎 (3房)
 $2995万
 $25,400/呎
-(16年-06月-05日)</t>
+(16年-06月-06日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -7196,7 +7196,7 @@
           <t>D | 1702呎 (4+房)
 $4000万
 $23,500/呎
-(16年-07月-12日)</t>
+(16年-07月-13日)</t>
         </is>
       </c>
     </row>
@@ -7227,7 +7227,7 @@
           <t>C | 1179呎 (3房)
 $2971万
 $25,200/呎
-(16年-06月-05日)</t>
+(16年-06月-06日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -7328,7 +7328,7 @@
           <t>A | 1735呎 (4+房)
 $6000万
 $34,582/呎
-(23年-05月-22日)</t>
+(23年-05月-23日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -7336,7 +7336,7 @@
           <t>B | 1023呎 (2房)
 $2568万
 $25,100/呎
-(16年-06月-05日)</t>
+(16年-06月-06日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -7367,7 +7367,7 @@
           <t>A | 1735呎 (4+房)
 $5850万
 $33,718/呎
-(24年-07月-07日)</t>
+(24年-07月-08日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -7375,7 +7375,7 @@
           <t>B | 1023呎 (2房)
 $2486万
 $24,300/呎
-(16年-02月-21日)</t>
+(16年-02月-22日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -7383,7 +7383,7 @@
           <t>C | 1179呎 (3房)
 $2720万
 $23,067/呎
-(16年-02月-21日)</t>
+(16年-02月-22日)</t>
         </is>
       </c>
       <c r="E19" s="20" t="inlineStr">
@@ -7406,7 +7406,7 @@
           <t>A | 1735呎 (4+房)
 $3990万
 $23,000/呎
-(16年-02月-21日)</t>
+(16年-02月-22日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -7414,7 +7414,7 @@
           <t>B | 1024呎 (2房)
 $3322万
 $32,440/呎
-(24年-05月-28日)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -7422,7 +7422,7 @@
           <t>C | 1179呎 (3房)
 $2841万
 $24,100/呎
-(16年-03月-01日)</t>
+(16年-03月-02日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -7445,7 +7445,7 @@
           <t>A | 1735呎 (4+房)
 $3933万
 $22,671/呎
-(16年-02月-21日)</t>
+(16年-02月-22日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -7453,7 +7453,7 @@
           <t>B | 1024呎 (2房)
 $3241万
 $31,649/呎
-(24年-05月-01日)</t>
+(24年-05月-02日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -7461,7 +7461,7 @@
           <t>C | 1179呎 (3房)
 $2724万
 $23,100/呎
-(16年-02月-21日)</t>
+(16年-02月-22日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -7492,7 +7492,7 @@
           <t>B | 1024呎 (2房)
 $3190万
 $31,155/呎
-(24年-10月-15日)</t>
+(24年-10月-16日)</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -7523,7 +7523,7 @@
           <t>A | 1735呎 (4+房)
 $5280万
 $30,432/呎
-(24年-10月-31日)</t>
+(24年-11月-01日)</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -7562,7 +7562,7 @@
           <t>A | 1735呎 (4+房)
 $5148万
 $29,671/呎
-(24年-11月-03日)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -7570,7 +7570,7 @@
           <t>B | 1024呎 (2房)
 $2435万
 $23,776/呎
-(16年-02月-21日)</t>
+(16年-02月-22日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -7578,7 +7578,7 @@
           <t>C | 1179呎 (3房)
 $2688万
 $22,800/呎
-(16年-02月-21日)</t>
+(16年-02月-22日)</t>
         </is>
       </c>
       <c r="E24" s="20" t="inlineStr">
@@ -7601,7 +7601,7 @@
           <t>A | 1735呎 (4+房)
 $3904万
 $22,500/呎
-(16年-04月-27日)</t>
+(16年-04月-28日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -7609,7 +7609,7 @@
           <t>B | 1023呎 (2房)
 $2424万
 $23,700/呎
-(16年-02月-24日)</t>
+(16年-02月-25日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -7617,7 +7617,7 @@
           <t>C | 1179呎 (3房)
 $2650万
 $22,473/呎
-(16年-01月-23日)</t>
+(16年-01月-24日)</t>
         </is>
       </c>
       <c r="E25" s="20" t="inlineStr">
@@ -7648,7 +7648,7 @@
           <t>B | 1024呎 (2房)
 $3038万
 $29,671/呎
-(24年-04月-23日)</t>
+(24年-04月-24日)</t>
         </is>
       </c>
       <c r="D26" s="20" t="inlineStr">
@@ -7679,7 +7679,7 @@
           <t>A | 1735呎 (4+房)
 $4945万
 $28,500/呎
-(26年-02月-05日)</t>
+(26年-02月-06日)</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -7695,7 +7695,7 @@
           <t>C | 1179呎 (3房)
 $2720万
 $23,070/呎
-(16年-03月-17日)</t>
+(16年-03月-18日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -7703,7 +7703,7 @@
           <t>D | 1702呎 (4+房)
 $3642万
 $21,400/呎
-(16年-06月-19日)</t>
+(16年-06月-20日)</t>
         </is>
       </c>
     </row>
@@ -7734,7 +7734,7 @@
           <t>C | 1129呎 (3房)
 $3048万
 $27,000/呎
-(16年-02月-21日)</t>
+(16年-02月-22日)</t>
         </is>
       </c>
       <c r="E28" s="22" t="inlineStr">
@@ -7742,7 +7742,7 @@
           <t>D | 1639呎 (4+房)
 $4105万
 $25,047/呎
-(16年-02月-21日)</t>
+(16年-02月-22日)</t>
         </is>
       </c>
     </row>
